--- a/dynamical_DE_nonfid/data/combined/pelg+jmul-w0wacdm-free.xlsx
+++ b/dynamical_DE_nonfid/data/combined/pelg+jmul-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>541125.9524420125</v>
+        <v>541125.9524419835</v>
       </c>
       <c r="C2" t="n">
-        <v>-962286.5830076972</v>
+        <v>-962286.58300759</v>
       </c>
       <c r="D2" t="n">
-        <v>74767.92812979876</v>
+        <v>74767.92812974514</v>
       </c>
       <c r="E2" t="n">
-        <v>216682.9006585222</v>
+        <v>216682.9006585107</v>
       </c>
       <c r="F2" t="n">
-        <v>-12113.26550992078</v>
+        <v>-12113.2655099096</v>
       </c>
       <c r="G2" t="n">
-        <v>-21772.73991902658</v>
+        <v>-21772.73991902544</v>
       </c>
       <c r="H2" t="n">
-        <v>-8254.353953432146</v>
+        <v>-8254.353953431062</v>
       </c>
       <c r="I2" t="n">
-        <v>-21677.05381659991</v>
+        <v>-21677.05381660284</v>
       </c>
       <c r="J2" t="n">
-        <v>-2287.01282875112</v>
+        <v>-2287.012828752204</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-962286.583007433</v>
+        <v>-962286.583007353</v>
       </c>
       <c r="C3" t="n">
-        <v>2432928.033121568</v>
+        <v>2432928.033121342</v>
       </c>
       <c r="D3" t="n">
-        <v>-395984.3302257696</v>
+        <v>-395984.3302256315</v>
       </c>
       <c r="E3" t="n">
-        <v>-409492.1216087382</v>
+        <v>-409492.1216087118</v>
       </c>
       <c r="F3" t="n">
-        <v>41311.50131038101</v>
+        <v>41311.50131033476</v>
       </c>
       <c r="G3" t="n">
-        <v>41296.03384957019</v>
+        <v>41296.03384956668</v>
       </c>
       <c r="H3" t="n">
-        <v>20765.31669099497</v>
+        <v>20765.31669099272</v>
       </c>
       <c r="I3" t="n">
-        <v>12248.70487031805</v>
+        <v>12248.70487032073</v>
       </c>
       <c r="J3" t="n">
-        <v>518.7605744543176</v>
+        <v>518.7605744566263</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74767.92812948104</v>
+        <v>74767.92812950113</v>
       </c>
       <c r="C4" t="n">
-        <v>-395984.3302252966</v>
+        <v>-395984.330225352</v>
       </c>
       <c r="D4" t="n">
-        <v>276330.1540230138</v>
+        <v>276330.1540230311</v>
       </c>
       <c r="E4" t="n">
-        <v>46627.79143618778</v>
+        <v>46627.79143619537</v>
       </c>
       <c r="F4" t="n">
-        <v>-95584.40059259915</v>
+        <v>-95584.40059260206</v>
       </c>
       <c r="G4" t="n">
-        <v>-5190.557836020182</v>
+        <v>-5190.55783602102</v>
       </c>
       <c r="H4" t="n">
-        <v>-3927.854260140419</v>
+        <v>-3927.854260140969</v>
       </c>
       <c r="I4" t="n">
-        <v>14871.72392071241</v>
+        <v>14871.72392071295</v>
       </c>
       <c r="J4" t="n">
-        <v>4981.910461541867</v>
+        <v>4981.910461542119</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>216682.9006583844</v>
+        <v>216682.9006583544</v>
       </c>
       <c r="C5" t="n">
-        <v>-409492.1216086409</v>
+        <v>-409492.121608561</v>
       </c>
       <c r="D5" t="n">
-        <v>46627.79143633753</v>
+        <v>46627.79143629163</v>
       </c>
       <c r="E5" t="n">
-        <v>100003.5722316535</v>
+        <v>100003.5722316436</v>
       </c>
       <c r="F5" t="n">
-        <v>-16712.06662738194</v>
+        <v>-16712.06662736582</v>
       </c>
       <c r="G5" t="n">
-        <v>-9786.782431668486</v>
+        <v>-9786.782431667121</v>
       </c>
       <c r="H5" t="n">
-        <v>-3713.008885697506</v>
+        <v>-3713.008885696716</v>
       </c>
       <c r="I5" t="n">
-        <v>-7535.643318250472</v>
+        <v>-7535.643318250953</v>
       </c>
       <c r="J5" t="n">
-        <v>-818.1740199134275</v>
+        <v>-818.1740199140906</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-12113.26550991807</v>
+        <v>-12113.26550993753</v>
       </c>
       <c r="C6" t="n">
-        <v>41311.50131044014</v>
+        <v>41311.50131048229</v>
       </c>
       <c r="D6" t="n">
-        <v>-95584.40059263998</v>
+        <v>-95584.40059266167</v>
       </c>
       <c r="E6" t="n">
-        <v>-16712.06662737932</v>
+        <v>-16712.06662738543</v>
       </c>
       <c r="F6" t="n">
-        <v>79943.63937320636</v>
+        <v>79943.63937321541</v>
       </c>
       <c r="G6" t="n">
-        <v>3760.976029157155</v>
+        <v>3760.976029158074</v>
       </c>
       <c r="H6" t="n">
-        <v>424.6991137548075</v>
+        <v>424.6991137552112</v>
       </c>
       <c r="I6" t="n">
-        <v>-952.3098635924478</v>
+        <v>-952.309863592043</v>
       </c>
       <c r="J6" t="n">
-        <v>-1576.848092517266</v>
+        <v>-1576.848092517497</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-21772.73991898988</v>
+        <v>-21772.73991898716</v>
       </c>
       <c r="C7" t="n">
-        <v>41296.03384951867</v>
+        <v>41296.03384951041</v>
       </c>
       <c r="D7" t="n">
-        <v>-5190.557836032061</v>
+        <v>-5190.557836027511</v>
       </c>
       <c r="E7" t="n">
-        <v>-9786.782431658014</v>
+        <v>-9786.78243165707</v>
       </c>
       <c r="F7" t="n">
-        <v>3760.97602915398</v>
+        <v>3760.976029152655</v>
       </c>
       <c r="G7" t="n">
-        <v>1126.756981970004</v>
+        <v>1126.756981969888</v>
       </c>
       <c r="H7" t="n">
-        <v>360.9351268865757</v>
+        <v>360.9351268864927</v>
       </c>
       <c r="I7" t="n">
-        <v>984.8866095288322</v>
+        <v>984.8866095289557</v>
       </c>
       <c r="J7" t="n">
-        <v>102.460100016211</v>
+        <v>102.460100016286</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-8254.353953403128</v>
+        <v>-8254.353953401387</v>
       </c>
       <c r="C8" t="n">
-        <v>20765.31669094816</v>
+        <v>20765.31669094391</v>
       </c>
       <c r="D8" t="n">
-        <v>-3927.854260142546</v>
+        <v>-3927.854260139817</v>
       </c>
       <c r="E8" t="n">
-        <v>-3713.008885686545</v>
+        <v>-3713.008885686012</v>
       </c>
       <c r="F8" t="n">
-        <v>424.6991137522733</v>
+        <v>424.6991137512025</v>
       </c>
       <c r="G8" t="n">
-        <v>360.9351268857573</v>
+        <v>360.9351268856765</v>
       </c>
       <c r="H8" t="n">
-        <v>192.5630145059008</v>
+        <v>192.5630145058589</v>
       </c>
       <c r="I8" t="n">
-        <v>75.09060087903705</v>
+        <v>75.09060087903454</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.414066974006641</v>
+        <v>-2.414066973970414</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-21677.05381655461</v>
+        <v>-21677.05381654897</v>
       </c>
       <c r="C9" t="n">
-        <v>12248.70487025353</v>
+        <v>12248.70487023208</v>
       </c>
       <c r="D9" t="n">
-        <v>14871.72392069893</v>
+        <v>14871.72392070747</v>
       </c>
       <c r="E9" t="n">
-        <v>-7535.643318240111</v>
+        <v>-7535.643318237863</v>
       </c>
       <c r="F9" t="n">
-        <v>-952.3098635945159</v>
+        <v>-952.3098635955018</v>
       </c>
       <c r="G9" t="n">
-        <v>984.8866095285922</v>
+        <v>984.886609528385</v>
       </c>
       <c r="H9" t="n">
-        <v>75.0906008798259</v>
+        <v>75.0906008796114</v>
       </c>
       <c r="I9" t="n">
-        <v>3704.306962004959</v>
+        <v>3704.306962005481</v>
       </c>
       <c r="J9" t="n">
-        <v>716.6043025239524</v>
+        <v>716.6043025241099</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-2287.012828735605</v>
+        <v>-2287.012828733187</v>
       </c>
       <c r="C10" t="n">
-        <v>518.7605744292382</v>
+        <v>518.7605744214509</v>
       </c>
       <c r="D10" t="n">
-        <v>4981.910461541279</v>
+        <v>4981.910461544514</v>
       </c>
       <c r="E10" t="n">
-        <v>-818.1740199083185</v>
+        <v>-818.1740199074319</v>
       </c>
       <c r="F10" t="n">
-        <v>-1576.848092518423</v>
+        <v>-1576.84809251906</v>
       </c>
       <c r="G10" t="n">
-        <v>102.4601000157421</v>
+        <v>102.4601000156446</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.414066974036659</v>
+        <v>-2.414066974113289</v>
       </c>
       <c r="I10" t="n">
-        <v>716.6043025234237</v>
+        <v>716.6043025235435</v>
       </c>
       <c r="J10" t="n">
-        <v>196.8641534574673</v>
+        <v>196.8641534575184</v>
       </c>
     </row>
   </sheetData>
